--- a/data/20250728_前端咖啡订单.xlsx
+++ b/data/20250728_前端咖啡订单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,34 +476,34 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>处理时间</t>
+          <t>实际价格</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W1202507281116498680</t>
+          <t>W1202507281435194317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15151365498.0</t>
+          <t>15851301568.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>朱杰</t>
+          <t>高亦超</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>数智化支撑中心</t>
+          <t>工程建设部</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-07-28 11:16:49</t>
+          <t>2025-07-28 14:35:19</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -526,58 +526,158 @@
           <t>备货中</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>W1202507281402403904</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>15151365498.0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>朱杰</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>数智化支撑中心</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-07-28 14:02:40</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>咖啡测试 请勿点击</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>去冰</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>备货中</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W1202507281116498680</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>15151365498.0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>朱杰</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>数智化支撑中心</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-07-28 11:16:49</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>咖啡测试 请勿点击</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>W1202507281023566821</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>15151365498.0</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>朱杰</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>数智化支撑中心</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2025-07-28 10:23:56</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>咖啡测试 请勿点击</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>备货中</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
